--- a/artfynd/A 29553-2019 artfynd.xlsx
+++ b/artfynd/A 29553-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29553-2019 artfynd.xlsx
+++ b/artfynd/A 29553-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9554,6 +9554,109 @@
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>114928142</v>
+      </c>
+      <c r="B72" t="n">
+        <v>91506</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Nyboholm, Sm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>530936</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6362567</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Ökna</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Lars Tidemalm</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Lars Tidemalm</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
